--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>36:36</t>
+          <t>26:33</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
     </row>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>2</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>69:38</t>
+          <t>29:39</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>34:47</t>
+          <t>24:48</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>47:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,17 +2039,17 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>53:12</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>24:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -2511,16 +2511,16 @@
         <v>25</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>9</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57:05</t>
+          <t>27:06</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -2707,16 +2707,16 @@
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>76:31</t>
+          <t>36:31</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -3043,16 +3043,16 @@
         <v>86</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>25</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>43:39</t>
+          <t>23:41</t>
         </is>
       </c>
       <c r="AN31" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="AN32" t="n">
@@ -3900,10 +3900,10 @@
         <v>12</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>63:11</t>
+          <t>23:13</t>
         </is>
       </c>
       <c r="AN33" t="n">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>39:17</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
     </row>
@@ -4292,16 +4292,16 @@
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>34:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>4</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>38:16</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>29:12</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>27:23</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -5272,16 +5272,16 @@
         <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>37:44</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -5664,7 +5664,7 @@
         <v>23</v>
       </c>
       <c r="T42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>45:23</t>
+          <t>25:20</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
     </row>
@@ -6000,16 +6000,16 @@
         <v>145</v>
       </c>
       <c r="T44" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>16</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>2</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2511,16 +2511,16 @@
         <v>25</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>9</v>
@@ -2707,16 +2707,16 @@
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -3043,16 +3043,16 @@
         <v>86</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X26" t="n">
         <v>25</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3900,10 +3900,10 @@
         <v>12</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -4292,16 +4292,16 @@
         <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>4</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>1</v>
@@ -5272,16 +5272,16 @@
         <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5664,7 +5664,7 @@
         <v>23</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6000,16 +6000,16 @@
         <v>145</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X44" t="n">
         <v>16</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_392_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>15</v>
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3055,14 +3055,14 @@
         <v>6</v>
       </c>
       <c r="X26" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3520,14 +3520,14 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA31" t="n">
@@ -3912,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -5284,10 +5284,10 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6012,10 +6012,10 @@
         <v>7</v>
       </c>
       <c r="X44" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
